--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,616 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129501572</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Barrskog NÖÖ om Långeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>461531</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6410092</v>
+      </c>
+      <c r="S3" t="n">
+        <v>18</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129501587</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Barrskog NÖÖ om Långeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>461577</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6410023</v>
+      </c>
+      <c r="S4" t="n">
+        <v>16</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129501564</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Barrskog NÖÖ om Långeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>461537</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6410061</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129501513</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97182</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>232</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedsäckmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Calypogeia suecica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Barrskog NÖÖ om Långeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>461577</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6410023</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129501477</v>
+      </c>
+      <c r="B7" t="n">
+        <v>95948</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Barrskog NÖÖ om Långeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>461592</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6410061</v>
+      </c>
+      <c r="S7" t="n">
+        <v>18</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>129501513</v>
       </c>
       <c r="B6" t="n">
-        <v>97182</v>
+        <v>97186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129501477</v>
       </c>
       <c r="B7" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>129501513</v>
       </c>
       <c r="B6" t="n">
-        <v>97186</v>
+        <v>97194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129501477</v>
       </c>
       <c r="B7" t="n">
-        <v>95952</v>
+        <v>95960</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1164,32 +1164,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129501513</v>
+        <v>129501477</v>
       </c>
       <c r="B6" t="n">
-        <v>97194</v>
+        <v>95960</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedsäckmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calypogeia suecica</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med groddkorn</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461577</v>
+        <v>461592</v>
       </c>
       <c r="R6" t="n">
-        <v>6410023</v>
+        <v>6410061</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,32 +1281,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129501477</v>
+        <v>129501513</v>
       </c>
       <c r="B7" t="n">
-        <v>95960</v>
+        <v>97194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>232</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedsäckmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Calypogeia suecica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461592</v>
+        <v>461577</v>
       </c>
       <c r="R7" t="n">
-        <v>6410061</v>
+        <v>6410023</v>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1164,32 +1164,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129501477</v>
+        <v>129501513</v>
       </c>
       <c r="B6" t="n">
-        <v>95960</v>
+        <v>97197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>232</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedsäckmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Calypogeia suecica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461592</v>
+        <v>461577</v>
       </c>
       <c r="R6" t="n">
-        <v>6410061</v>
+        <v>6410023</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,32 +1281,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129501513</v>
+        <v>129501477</v>
       </c>
       <c r="B7" t="n">
-        <v>97194</v>
+        <v>95963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>232</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedsäckmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calypogeia suecica</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med groddkorn</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461577</v>
+        <v>461592</v>
       </c>
       <c r="R7" t="n">
-        <v>6410023</v>
+        <v>6410061</v>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1164,32 +1164,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129501513</v>
+        <v>129501477</v>
       </c>
       <c r="B6" t="n">
-        <v>97197</v>
+        <v>95963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedsäckmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calypogeia suecica</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med groddkorn</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461577</v>
+        <v>461592</v>
       </c>
       <c r="R6" t="n">
-        <v>6410023</v>
+        <v>6410061</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,32 +1281,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129501477</v>
+        <v>129501513</v>
       </c>
       <c r="B7" t="n">
-        <v>95963</v>
+        <v>97197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>232</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedsäckmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Calypogeia suecica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461592</v>
+        <v>461577</v>
       </c>
       <c r="R7" t="n">
-        <v>6410061</v>
+        <v>6410023</v>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1164,32 +1164,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129501477</v>
+        <v>129501513</v>
       </c>
       <c r="B6" t="n">
-        <v>95963</v>
+        <v>97197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>232</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedsäckmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Calypogeia suecica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461592</v>
+        <v>461577</v>
       </c>
       <c r="R6" t="n">
-        <v>6410061</v>
+        <v>6410023</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,32 +1281,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129501513</v>
+        <v>129501477</v>
       </c>
       <c r="B7" t="n">
-        <v>97197</v>
+        <v>95963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>232</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedsäckmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calypogeia suecica</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med groddkorn</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461577</v>
+        <v>461592</v>
       </c>
       <c r="R7" t="n">
-        <v>6410023</v>
+        <v>6410061</v>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>129501513</v>
       </c>
       <c r="B6" t="n">
-        <v>97197</v>
+        <v>97226</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129501477</v>
       </c>
       <c r="B7" t="n">
-        <v>95963</v>
+        <v>95992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>129501513</v>
       </c>
       <c r="B6" t="n">
-        <v>97226</v>
+        <v>97238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129501477</v>
       </c>
       <c r="B7" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>129501513</v>
       </c>
       <c r="B6" t="n">
-        <v>97238</v>
+        <v>97239</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129501477</v>
       </c>
       <c r="B7" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>129501513</v>
       </c>
       <c r="B6" t="n">
-        <v>97239</v>
+        <v>97244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129501477</v>
       </c>
       <c r="B7" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1164,32 +1164,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129501513</v>
+        <v>129501477</v>
       </c>
       <c r="B6" t="n">
-        <v>97244</v>
+        <v>96010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedsäckmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calypogeia suecica</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med groddkorn</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461577</v>
+        <v>461592</v>
       </c>
       <c r="R6" t="n">
-        <v>6410023</v>
+        <v>6410061</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,32 +1281,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129501477</v>
+        <v>129501513</v>
       </c>
       <c r="B7" t="n">
-        <v>96010</v>
+        <v>97244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>232</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedsäckmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Calypogeia suecica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461592</v>
+        <v>461577</v>
       </c>
       <c r="R7" t="n">
-        <v>6410061</v>
+        <v>6410023</v>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1164,32 +1164,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129501477</v>
+        <v>129501513</v>
       </c>
       <c r="B6" t="n">
-        <v>96010</v>
+        <v>97244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>232</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedsäckmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Calypogeia suecica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461592</v>
+        <v>461577</v>
       </c>
       <c r="R6" t="n">
-        <v>6410061</v>
+        <v>6410023</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,32 +1281,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129501513</v>
+        <v>129501477</v>
       </c>
       <c r="B7" t="n">
-        <v>97244</v>
+        <v>96010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>232</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedsäckmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calypogeia suecica</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med groddkorn</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461577</v>
+        <v>461592</v>
       </c>
       <c r="R7" t="n">
-        <v>6410023</v>
+        <v>6410061</v>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>129501513</v>
       </c>
       <c r="B6" t="n">
-        <v>97244</v>
+        <v>97248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129501477</v>
       </c>
       <c r="B7" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>129501513</v>
       </c>
       <c r="B6" t="n">
-        <v>97248</v>
+        <v>97250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>129501477</v>
       </c>
       <c r="B7" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1164,32 +1164,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129501513</v>
+        <v>129501477</v>
       </c>
       <c r="B6" t="n">
-        <v>97250</v>
+        <v>96016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedsäckmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calypogeia suecica</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med groddkorn</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461577</v>
+        <v>461592</v>
       </c>
       <c r="R6" t="n">
-        <v>6410023</v>
+        <v>6410061</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,32 +1281,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129501477</v>
+        <v>129501513</v>
       </c>
       <c r="B7" t="n">
-        <v>96016</v>
+        <v>97250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>232</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedsäckmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Calypogeia suecica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461592</v>
+        <v>461577</v>
       </c>
       <c r="R7" t="n">
-        <v>6410061</v>
+        <v>6410023</v>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -1164,32 +1164,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129501477</v>
+        <v>129501513</v>
       </c>
       <c r="B6" t="n">
-        <v>96016</v>
+        <v>97260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>232</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedsäckmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Calypogeia suecica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461592</v>
+        <v>461577</v>
       </c>
       <c r="R6" t="n">
-        <v>6410061</v>
+        <v>6410023</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,32 +1281,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129501513</v>
+        <v>129501477</v>
       </c>
       <c r="B7" t="n">
-        <v>97250</v>
+        <v>96026</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>232</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedsäckmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calypogeia suecica</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med groddkorn</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461577</v>
+        <v>461592</v>
       </c>
       <c r="R7" t="n">
-        <v>6410023</v>
+        <v>6410061</v>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -675,54 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110367845</v>
+        <v>129501513</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>232</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedsäckmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Calypogeia suecica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Barrskog NÖÖ om Långeberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461530.041906761</v>
+        <v>461577</v>
       </c>
       <c r="R2" t="n">
-        <v>6410091.781775708</v>
+        <v>6410023</v>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129501572</v>
+        <v>110367845</v>
       </c>
       <c r="B3" t="n">
-        <v>4779</v>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,39 +803,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Barrskog NÖÖ om Långeberg, Sm</t>
@@ -868,22 +858,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,16 +884,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -920,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129501587</v>
+        <v>129501477</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,37 +911,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -970,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461577</v>
+        <v>461592</v>
       </c>
       <c r="R4" t="n">
-        <v>6410023</v>
+        <v>6410061</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129501564</v>
+        <v>129501587</v>
       </c>
       <c r="B5" t="n">
-        <v>5197</v>
+        <v>5179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,21 +1028,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1092,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461537</v>
+        <v>461577</v>
       </c>
       <c r="R5" t="n">
-        <v>6410061</v>
+        <v>6410023</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1137,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,43 +1139,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129501513</v>
+        <v>129501572</v>
       </c>
       <c r="B6" t="n">
-        <v>97260</v>
+        <v>4781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedsäckmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calypogeia suecica</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1209,13 +1189,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461577</v>
+        <v>461531</v>
       </c>
       <c r="R6" t="n">
-        <v>6410023</v>
+        <v>6410092</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,6 +1245,16 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1281,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129501477</v>
+        <v>129501564</v>
       </c>
       <c r="B7" t="n">
-        <v>96026</v>
+        <v>5199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,32 +1282,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1326,13 +1321,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461592</v>
+        <v>461537</v>
       </c>
       <c r="R7" t="n">
         <v>6410061</v>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1366,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 47402-2025 artfynd.xlsx
+++ b/artfynd/A 47402-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129501513</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110367845</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129501477</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129501587</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,6 +1293,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129501572</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1390,8 +1420,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129501564</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>